--- a/ig/nr-update-location-identifier/ValueSet-fr-core-practitioner-role-profession.xlsx
+++ b/ig/nr-update-location-identifier/ValueSet-fr-core-practitioner-role-profession.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-G15-Professi" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-R95-UsagerTi" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE-R94-Professi" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE-R291-AutrePr" r:id="rId7" sheetId="5"/>
+    <sheet name="Include from TRE_G15-Professi" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R95-UsagerTi" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from TRE_R94-Professi" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from TRE_R291-AutrePr" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:16:44+00:00</t>
+    <t>2023-12-20T16:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
